--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.5180937884974</v>
+        <v>4.959190240630828</v>
       </c>
       <c r="D2" t="n">
-        <v>29.74573731901517</v>
+        <v>4.833682314339966</v>
       </c>
       <c r="E2" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F2" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.87330726271864</v>
+        <v>4.529412430191779</v>
       </c>
       <c r="D3" t="n">
-        <v>29.36384569512539</v>
+        <v>4.771624925457877</v>
       </c>
       <c r="E3" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F3" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.57801051712438</v>
+        <v>3.181426709032712</v>
       </c>
       <c r="D4" t="n">
-        <v>16.30722680967619</v>
+        <v>2.64992435657238</v>
       </c>
       <c r="E4" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F4" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.14343517096703</v>
+        <v>1.973308215282143</v>
       </c>
       <c r="D5" t="n">
-        <v>13.50102876738576</v>
+        <v>2.193917174700185</v>
       </c>
       <c r="E5" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F5" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.09146006770501</v>
+        <v>2.777362261002065</v>
       </c>
       <c r="D6" t="n">
-        <v>15.61874300799136</v>
+        <v>2.538045738798596</v>
       </c>
       <c r="E6" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F6" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.464513966912154</v>
+        <v>1.050483519623225</v>
       </c>
       <c r="D7" t="n">
-        <v>9.020039418489874</v>
+        <v>1.465756405504605</v>
       </c>
       <c r="E7" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F7" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.76565658623538</v>
+        <v>0.4494191952632492</v>
       </c>
       <c r="D8" t="n">
-        <v>19.65775228457693</v>
+        <v>3.194384746243751</v>
       </c>
       <c r="E8" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F8" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.9269722280108</v>
+        <v>3.888132987051755</v>
       </c>
       <c r="D9" t="n">
-        <v>32.29752640660602</v>
+        <v>5.248348041073478</v>
       </c>
       <c r="E9" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F9" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.34034777094501</v>
+        <v>2.980306512778564</v>
       </c>
       <c r="D10" t="n">
-        <v>14.79039347719611</v>
+        <v>2.403438940044368</v>
       </c>
       <c r="E10" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F10" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4.892044436166954</v>
+        <v>0.7949572208771299</v>
       </c>
       <c r="D11" t="n">
-        <v>19.11156223440903</v>
+        <v>3.105628863091467</v>
       </c>
       <c r="E11" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F11" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.572689915254749</v>
+        <v>1.393062111228897</v>
       </c>
       <c r="D12" t="n">
-        <v>7.672966629422733</v>
+        <v>1.246857077281194</v>
       </c>
       <c r="E12" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F12" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.00098601571336</v>
+        <v>4.062660227553422</v>
       </c>
       <c r="D13" t="n">
-        <v>19.88694515744271</v>
+        <v>3.23162858808444</v>
       </c>
       <c r="E13" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F13" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.9406276172647</v>
+        <v>2.752851987805514</v>
       </c>
       <c r="D14" t="n">
-        <v>39.27273236136667</v>
+        <v>6.381819008722085</v>
       </c>
       <c r="E14" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F14" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.19276453055848</v>
+        <v>2.793824236215753</v>
       </c>
       <c r="D15" t="n">
-        <v>44.2315556724561</v>
+        <v>7.187627796774117</v>
       </c>
       <c r="E15" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F15" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.83357612646689</v>
+        <v>2.89795612055087</v>
       </c>
       <c r="D16" t="n">
-        <v>19.77071992146852</v>
+        <v>3.212741987238634</v>
       </c>
       <c r="E16" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F16" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.86692473554286</v>
+        <v>3.065875269525714</v>
       </c>
       <c r="D17" t="n">
-        <v>27.99548535032033</v>
+        <v>4.549266369427054</v>
       </c>
       <c r="E17" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F17" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>13.26632566863148</v>
+        <v>2.155777921152616</v>
       </c>
       <c r="D18" t="n">
-        <v>38.68911198630961</v>
+        <v>6.286980697775311</v>
       </c>
       <c r="E18" t="n">
-        <v>7.634608198573879</v>
+        <v>1.240623832268255</v>
       </c>
       <c r="F18" t="n">
-        <v>10.54606686507641</v>
+        <v>1.713735865574917</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
